--- a/data/trans_orig/IP18A01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP18A01-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42036</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48405</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44678</t>
+          <t>44693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50704</t>
+          <t>50700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89735</t>
+          <t>89305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97930</t>
+          <t>98072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25964</t>
+          <t>25607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75402</t>
+          <t>75770</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85355</t>
+          <t>85322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82740</t>
+          <t>83950</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92132</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162258</t>
+          <t>162615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175425</t>
+          <t>175572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56729</t>
+          <t>57046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62678</t>
+          <t>62680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60914</t>
+          <t>61486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66529</t>
+          <t>66516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120965</t>
+          <t>120667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127939</t>
+          <t>127948</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59864</t>
+          <t>59719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66212</t>
+          <t>66066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59049</t>
+          <t>58997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65885</t>
+          <t>65903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122303</t>
+          <t>121889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131013</t>
+          <t>131231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31459</t>
+          <t>31462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55865</t>
+          <t>56382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62381</t>
+          <t>62374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44850</t>
+          <t>44343</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50398</t>
+          <t>50399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45158</t>
+          <t>44611</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50190</t>
+          <t>50185</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91117</t>
+          <t>92136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99363</t>
+          <t>99453</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11893</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24863</t>
+          <t>24238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109728</t>
+          <t>109570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118099</t>
+          <t>118173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107367</t>
+          <t>107884</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>117567</t>
+          <t>117768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220608</t>
+          <t>221233</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>234350</t>
+          <t>233489</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>24406</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27473</t>
+          <t>27796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29320</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46917</t>
+          <t>48158</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95702</t>
+          <t>96236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108586</t>
+          <t>108620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>106102</t>
+          <t>105779</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119530</t>
+          <t>119448</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>207300</t>
+          <t>206059</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>224897</t>
+          <t>224272</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>42169</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62606</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41419</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64291</t>
+          <t>64459</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87795</t>
+          <t>88837</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>118659</t>
+          <t>120141</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>535412</t>
+          <t>534320</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>557018</t>
+          <t>555849</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>559723</t>
+          <t>559555</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>582595</t>
+          <t>582366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1103373</t>
+          <t>1101891</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1134237</t>
+          <t>1133195</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40268</t>
+          <t>40240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>47094</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41665</t>
+          <t>40992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>50320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84836</t>
+          <t>84160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>95515</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85219</t>
+          <t>85068</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93022</t>
+          <t>92805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84700</t>
+          <t>84890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93354</t>
+          <t>93427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173270</t>
+          <t>173077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184693</t>
+          <t>184503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57366</t>
+          <t>57825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65352</t>
+          <t>65420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55054</t>
+          <t>54702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64975</t>
+          <t>64492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116624</t>
+          <t>115939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128807</t>
+          <t>128113</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62120</t>
+          <t>62086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69723</t>
+          <t>70023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67574</t>
+          <t>68393</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76487</t>
+          <t>76405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133747</t>
+          <t>134368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144559</t>
+          <t>145362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32318</t>
+          <t>31852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37909</t>
+          <t>37897</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37147</t>
+          <t>37127</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42601</t>
+          <t>42607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71947</t>
+          <t>71930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>79764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18689</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43639</t>
+          <t>43743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51715</t>
+          <t>51640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46804</t>
+          <t>47288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56080</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94925</t>
+          <t>94304</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106226</t>
+          <t>105809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>24115</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>25738</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26727</t>
+          <t>25696</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45007</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110563</t>
+          <t>110905</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123703</t>
+          <t>123755</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118530</t>
+          <t>117368</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>131172</t>
+          <t>131329</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>233119</t>
+          <t>233920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>251399</t>
+          <t>252430</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>25757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23991</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41245</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124017</t>
+          <t>126202</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138327</t>
+          <t>138689</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141647</t>
+          <t>141773</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152894</t>
+          <t>153011</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>270789</t>
+          <t>270913</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288043</t>
+          <t>288011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>53923</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>77802</t>
+          <t>77796</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>57925</t>
+          <t>58366</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>84753</t>
+          <t>85503</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>118617</t>
+          <t>119009</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>156587</t>
+          <t>155819</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>586002</t>
+          <t>586008</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>610925</t>
+          <t>609881</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>622908</t>
+          <t>622158</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>649736</t>
+          <t>649295</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1214878</t>
+          <t>1215646</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1252848</t>
+          <t>1252456</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>826</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42744</t>
+          <t>43175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49715</t>
+          <t>49647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47324</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>53799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92796</t>
+          <t>93806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102185</t>
+          <t>102467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75245</t>
+          <t>75333</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84143</t>
+          <t>83956</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79166</t>
+          <t>79213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88488</t>
+          <t>88731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158256</t>
+          <t>157620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>170608</t>
+          <t>170409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20719</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51805</t>
+          <t>51941</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61222</t>
+          <t>61207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52628</t>
+          <t>52414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60008</t>
+          <t>60024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107310</t>
+          <t>108188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119634</t>
+          <t>119625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63681</t>
+          <t>64186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71593</t>
+          <t>71589</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72919</t>
+          <t>72701</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78516</t>
+          <t>78496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140722</t>
+          <t>140475</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149537</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>11123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>36355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41215</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36991</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>43472</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75989</t>
+          <t>75569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83595</t>
+          <t>83568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13949</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37631</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46956</t>
+          <t>47008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51931</t>
+          <t>52426</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84276</t>
+          <t>84090</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96825</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>24374</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24641</t>
+          <t>25127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25733</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43962</t>
+          <t>44388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86889</t>
+          <t>87172</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99553</t>
+          <t>99444</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87790</t>
+          <t>87304</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>100508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>180015</t>
+          <t>179589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>198244</t>
+          <t>196846</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27889</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142939</t>
+          <t>142142</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152572</t>
+          <t>152310</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151453</t>
+          <t>151416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>160973</t>
+          <t>161028</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>296267</t>
+          <t>297650</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310833</t>
+          <t>311217</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>49014</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73365</t>
+          <t>74082</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>47953</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>70654</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>102758</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>138204</t>
+          <t>135141</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>566980</t>
+          <t>566263</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>592284</t>
+          <t>591331</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>596921</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>622317</t>
+          <t>621728</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1171821</t>
+          <t>1174884</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1207281</t>
+          <t>1207267</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28818</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26688</t>
+          <t>27074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>344</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>415</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>16525</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>43274</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49609</t>
+          <t>49602</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31224</t>
+          <t>31203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18602</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87670</t>
+          <t>87530</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>96679</t>
+          <t>96545</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122152</t>
+          <t>121587</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>129056</t>
+          <t>129063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>213034</t>
+          <t>213304</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>223728</t>
+          <t>224190</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
